--- a/artfynd/A 9939-2021 artfynd.xlsx
+++ b/artfynd/A 9939-2021 artfynd.xlsx
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122035178</v>
+        <v>122034698</v>
       </c>
       <c r="B15" t="n">
-        <v>58079</v>
+        <v>57390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670733</v>
+        <v>670662</v>
       </c>
       <c r="R15" t="n">
-        <v>6562608</v>
+        <v>6562532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2272,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122034698</v>
+        <v>122035178</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>58079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>670662</v>
+        <v>670733</v>
       </c>
       <c r="R16" t="n">
-        <v>6562532</v>
+        <v>6562608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 9939-2021 artfynd.xlsx
+++ b/artfynd/A 9939-2021 artfynd.xlsx
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122034698</v>
+        <v>122035178</v>
       </c>
       <c r="B15" t="n">
-        <v>57390</v>
+        <v>58079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670662</v>
+        <v>670733</v>
       </c>
       <c r="R15" t="n">
-        <v>6562532</v>
+        <v>6562608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2272,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122035178</v>
+        <v>122034698</v>
       </c>
       <c r="B16" t="n">
-        <v>58079</v>
+        <v>57390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>670733</v>
+        <v>670662</v>
       </c>
       <c r="R16" t="n">
-        <v>6562608</v>
+        <v>6562532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 9939-2021 artfynd.xlsx
+++ b/artfynd/A 9939-2021 artfynd.xlsx
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122035178</v>
+        <v>122034698</v>
       </c>
       <c r="B15" t="n">
-        <v>58079</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670733</v>
+        <v>670662</v>
       </c>
       <c r="R15" t="n">
-        <v>6562608</v>
+        <v>6562532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2272,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122034698</v>
+        <v>122035178</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>58084</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>670662</v>
+        <v>670733</v>
       </c>
       <c r="R16" t="n">
-        <v>6562532</v>
+        <v>6562608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
